--- a/src/test/resources/testdata/Modules/12_Catalogue/Catalogue/01_CatalogueTest.xlsx
+++ b/src/test/resources/testdata/Modules/12_Catalogue/Catalogue/01_CatalogueTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\12_Catalogue\Catalogue\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{650B41E0-EEBE-49A1-9028-6FA9F985396D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9025E9A1-4582-4FF2-93BC-172B27937722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -182,12 +182,6 @@
 verify_productcode</t>
   </si>
   <si>
-    <t>clickon_pcc_category
-enter_productname
-hidekeyboard
-verify_snackbartext</t>
-  </si>
-  <si>
     <t>No data available</t>
   </si>
   <si>
@@ -215,6 +209,13 @@
   </si>
   <si>
     <t>1111</t>
+  </si>
+  <si>
+    <t>clickon_pcc_category
+enter_productname
+hidekeyboard
+verify_snackbartext
+navigatebacktodashboardpage</t>
   </si>
 </sst>
 </file>
@@ -1173,10 +1174,10 @@
         <v>3</v>
       </c>
       <c r="F1" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>36</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>28</v>
@@ -1205,13 +1206,13 @@
         <v>11</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>39</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
@@ -1245,7 +1246,7 @@
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>5</v>
@@ -1309,7 +1310,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
@@ -1323,7 +1324,7 @@
         <v>15</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
@@ -1332,7 +1333,7 @@
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>5</v>

--- a/src/test/resources/testdata/Modules/12_Catalogue/Catalogue/01_CatalogueTest.xlsx
+++ b/src/test/resources/testdata/Modules/12_Catalogue/Catalogue/01_CatalogueTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\12_Catalogue\Catalogue\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9025E9A1-4582-4FF2-93BC-172B27937722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A51B59-91E7-422A-8D33-BD541173D811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -163,10 +163,6 @@
   </si>
   <si>
     <t>PRODUCT_CODE</t>
-  </si>
-  <si>
-    <t>enter_productname
-verify_productcode</t>
   </si>
   <si>
     <t>Ambj001</t>
@@ -1174,10 +1170,10 @@
         <v>3</v>
       </c>
       <c r="F1" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>36</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>28</v>
@@ -1206,13 +1202,13 @@
         <v>11</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
@@ -1237,7 +1233,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -1246,13 +1242,13 @@
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -1266,7 +1262,7 @@
         <v>13</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
@@ -1295,16 +1291,16 @@
         <v>14</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>5</v>
@@ -1324,7 +1320,7 @@
         <v>15</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
@@ -1333,7 +1329,7 @@
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>5</v>

--- a/src/test/resources/testdata/Modules/12_Catalogue/Catalogue/01_CatalogueTest.xlsx
+++ b/src/test/resources/testdata/Modules/12_Catalogue/Catalogue/01_CatalogueTest.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\12_Catalogue\Catalogue\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A51B59-91E7-422A-8D33-BD541173D811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C462EA8-3DF1-445E-B4F6-BA9596ABB84A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TestCases!$A$1:$K$1</definedName>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="40">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -209,6 +210,12 @@
   <si>
     <t>clickon_pcc_category
 enter_productname
+hidekeyboard
+verify_snackbartext
+navigatebacktodashboardpage</t>
+  </si>
+  <si>
+    <t>enter_productname
 hidekeyboard
 verify_snackbartext
 navigatebacktodashboardpage</t>
@@ -1137,6 +1144,127 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{089D5808-B2AF-4105-BEF8-05FAA4CBE122}">
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.90625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48" style="7" customWidth="1"/>
+    <col min="5" max="5" width="29.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="29.453125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="19.81640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21.1796875" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30" style="2" customWidth="1"/>
+    <col min="11" max="11" width="10" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="8.90625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="174" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="5"/>
+      <c r="J3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K1" xr:uid="{089D5808-B2AF-4105-BEF8-05FAA4CBE122}"/>
+  <phoneticPr fontId="19" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1698A293-AF1C-4AAB-8D5E-31037D4FB677}">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1336,9 +1464,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1" xr:uid="{089D5808-B2AF-4105-BEF8-05FAA4CBE122}"/>
-  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>